--- a/GreenCartOrder.xlsx
+++ b/GreenCartOrder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skuma183\Pictures\GreenCart Order System\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GreenCartOrder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5E549E-D449-4951-ACA4-F04EFC1CAD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C80DBCA-9C9B-468E-A133-0041D11639D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5172" yWindow="4596" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Quantities</t>
   </si>
@@ -373,15 +373,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" customWidth="1"/>
-    <col min="2" max="2" width="26.36328125" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" customWidth="1"/>
-    <col min="4" max="4" width="18.90625" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -395,7 +395,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -409,28 +409,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
         <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
